--- a/tEST_TABLE.xlsx
+++ b/tEST_TABLE.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Masa_storage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{79C603CC-9E4A-439C-8923-79FE332DD1CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E51F59-654B-4CD1-AC50-966644AF2184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{35E78C6A-BA02-423C-9D63-4BECCE14973D}"/>
+    <workbookView xWindow="11850" yWindow="4920" windowWidth="17985" windowHeight="11595" xr2:uid="{35E78C6A-BA02-423C-9D63-4BECCE14973D}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -422,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4507F452-29B3-40F4-8691-A92612FD3479}">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" customWidth="1"/>
@@ -450,7 +450,7 @@
         <v>1958</v>
       </c>
       <c r="C2">
-        <v>515</v>
+        <v>1415</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -478,136 +478,10 @@
         <v>1489</v>
       </c>
       <c r="C4">
-        <v>616</v>
+        <v>916</v>
       </c>
       <c r="D4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>1596</v>
-      </c>
-      <c r="C5">
-        <v>151</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>1745</v>
-      </c>
-      <c r="C6">
-        <v>899</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>1658</v>
-      </c>
-      <c r="C7">
-        <v>499</v>
-      </c>
-      <c r="D7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>1365</v>
-      </c>
-      <c r="C8">
-        <v>456</v>
-      </c>
-      <c r="D8">
         <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>2000</v>
-      </c>
-      <c r="C9">
-        <v>489</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>1000</v>
-      </c>
-      <c r="C10">
-        <v>798</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>1500</v>
-      </c>
-      <c r="C11">
-        <v>1536</v>
-      </c>
-      <c r="D11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12">
-        <v>1230</v>
-      </c>
-      <c r="C12">
-        <v>1423</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13">
-        <v>1454</v>
-      </c>
-      <c r="C13">
-        <v>1454</v>
-      </c>
-      <c r="D13">
-        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/tEST_TABLE.xlsx
+++ b/tEST_TABLE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Masa_storage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E51F59-654B-4CD1-AC50-966644AF2184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3EECC0B-44A3-47D2-8C75-4903D608B275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11850" yWindow="4920" windowWidth="17985" windowHeight="11595" xr2:uid="{35E78C6A-BA02-423C-9D63-4BECCE14973D}"/>
   </bookViews>
@@ -467,7 +467,7 @@
         <v>414</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
